--- a/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_BUSINESS_METRICS.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Analytics/multiple_choice_sample_template_BUSINESS_METRICS.xlsx
@@ -453,19 +453,19 @@
         <v>CAC (Customer Acquisition Cost) được tính bằng tổng chi phí sales &amp; marketing chia cho số lượng khách hàng mới thu hút được trong một khoảng thời gian.</v>
       </c>
       <c r="E2" t="str">
+        <v>Tỷ lệ phần trăm khách hàng hủy bỏ dịch vụ và không tiếp tục gia hạn hợp đồng — tỷ lệ khách hàng rời bỏ</v>
+      </c>
+      <c r="F2" t="str">
         <v>Tổng chi phí trung bình để thu hút được một khách hàng mới sử dụng sản phẩm hoặc dịch vụ — chi phí thu hút khách hàng</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>Tổng chi phí tiền lương phải chi trả cho đội ngũ lập trình viên trong một tháng — chi phí phát triển</v>
+      </c>
+      <c r="H2" t="str">
         <v>Tổng doanh thu trung bình thu được từ một khách hàng trong suốt vòng đời của họ — doanh thu vòng đời khách hàng</v>
       </c>
-      <c r="G2" t="str">
-        <v>Tỷ lệ phần trăm khách hàng hủy bỏ dịch vụ và không tiếp tục gia hạn hợp đồng — tỷ lệ khách hàng rời bỏ</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Tổng chi phí tiền lương phải chi trả cho đội ngũ lập trình viên trong một tháng — chi phí phát triển</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>LTV (Lifetime Value) đo lường tổng giá trị kinh tế mà một khách hàng đóng góp cho doanh nghiệp trong suốt toàn bộ mối quan hệ của họ với sản phẩm/dịch vụ.</v>
       </c>
       <c r="E3" t="str">
+        <v>Số tiền tối đa mà khách hàng sẵn sàng trả tiền để mua sản phẩm trong một giao dịch đơn lẻ — giá trị giao dịch tối đa</v>
+      </c>
+      <c r="F3" t="str">
         <v>Tổng doanh thu hoặc lợi nhuận ròng dự kiến mà một khách hàng mang lại cho doanh nghiệp trong suốt thời gian họ gắn bó — giá trị vòng đời khách hàng</v>
       </c>
-      <c r="F3" t="str">
-        <v>Số tiền tối đa mà khách hàng sẵn sàng trả tiền để mua sản phẩm trong một giao dịch đơn lẻ — giá trị giao dịch tối đa</v>
-      </c>
       <c r="G3" t="str">
+        <v>Tỷ lệ phần trăm khách hàng đánh giá 5 sao cho ứng dụng trên kho ứng dụng di động — tỷ lệ đánh giá tốt</v>
+      </c>
+      <c r="H3" t="str">
         <v>Số năm trung bình mà một nhân viên sales làm việc gắn bó tại công ty — thời gian gắn bó của nhân sự</v>
       </c>
-      <c r="H3" t="str">
-        <v>Tỷ lệ phần trăm khách hàng đánh giá 5 sao cho ứng dụng trên kho ứng dụng di động — tỷ lệ đánh giá tốt</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -514,10 +514,10 @@
         <v>Số lượng khách hàng ngưng sử dụng dịch vụ trong kỳ chia cho tổng số khách hàng đầu kỳ — tỷ lệ khách hàng rời bỏ</v>
       </c>
       <c r="F4" t="str">
+        <v>Số lượng đơn hàng bị lỗi kỹ thuật chia cho tổng số đơn hàng đã giao thành công — tỷ lệ lỗi đơn hàng</v>
+      </c>
+      <c r="G4" t="str">
         <v>Số lượng khách hàng đăng ký mới trong kỳ chia cho tổng số khách hàng cũ — tỷ lệ tăng trưởng khách</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Số lượng đơn hàng bị lỗi kỹ thuật chia cho tổng số đơn hàng đã giao thành công — tỷ lệ lỗi đơn hàng</v>
       </c>
       <c r="H4" t="str">
         <v>Số tiền hoàn trả cho khách hàng chia cho tổng doanh thu bán hàng của doanh nghiệp — tỷ lệ hoàn tiền</v>
@@ -540,19 +540,19 @@
         <v>Phễu AARRR (Pirate Metrics) do Dave McClure đề xuất, là khung đo lường tiêu chuẩn cho các startup công nghệ để theo dõi toàn bộ vòng đời tương tác của khách hàng.</v>
       </c>
       <c r="E5" t="str">
+        <v>Analysis, Architecture, Requirements, Release, Retrospective — quy trình phát triển phần mềm</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Access, Authentication, Authorization, Audit, Administration — quy trình bảo mật thông tin</v>
+      </c>
+      <c r="G5" t="str">
         <v>Acquisition (Thu hút), Activation (Kích hoạt), Retention (Giữ chân), Referral (Giới thiệu), Revenue (Doanh thu) — phễu tăng trưởng AARRR</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>Advertising, Action, Research, Reporting, Review — quy trình tiếp thị trực tuyến</v>
       </c>
-      <c r="G5" t="str">
-        <v>Analysis, Architecture, Requirements, Release, Retrospective — quy trình phát triển phần mềm</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Access, Authentication, Authorization, Audit, Administration — quy trình bảo mật thông tin</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>AOV (Average Order Value) đo lường số tiền trung bình khách hàng chi tiêu cho mỗi lần mua hàng. Tăng AOV (qua up-sell, cross-sell) là cách nhanh để tăng doanh thu mà không cần tăng chi phí CAC.</v>
       </c>
       <c r="E6" t="str">
+        <v>Tổng số lượng sản phẩm bán ra chia cho tổng số lượng đơn hàng — số sản phẩm trung bình mỗi đơn</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Tổng số lượng khách hàng truy cập website chia cho tổng số đơn hàng được tạo — tỷ lệ chuyển đổi đơn</v>
+      </c>
+      <c r="G6" t="str">
         <v>Tổng doanh thu chia cho tổng số lượng đơn hàng trong một khoảng thời gian — giá trị đơn hàng trung bình</v>
       </c>
-      <c r="F6" t="str">
-        <v>Tổng số lượng sản phẩm bán ra chia cho tổng số lượng đơn hàng — số sản phẩm trung bình mỗi đơn</v>
-      </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Tổng chi phí quảng cáo trực tuyến chia cho tổng số đơn hàng thành công — chi phí quảng cáo mỗi đơn</v>
       </c>
-      <c r="H6" t="str">
-        <v>Tổng số lượng khách hàng truy cập website chia cho tổng số đơn hàng được tạo — tỷ lệ chuyển đổi đơn</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>MRR (Monthly Recurring Revenue) đo lường lượng doanh thu có tính chất lặp lại, dự đoán trước được mà doanh nghiệp SaaS nhận được hàng tháng từ các gói thuê bao hoạt động.</v>
       </c>
       <c r="E7" t="str">
+        <v>Mô hình nhận thầu xây dựng các công trình hạ tầng kỹ thuật quốc gia — nhận thầu xây dựng</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Mô hình đấu giá tài sản trực tuyến qua mạng internet — đấu giá tài sản</v>
+      </c>
+      <c r="G7" t="str">
         <v>Mô hình phần mềm dạng dịch vụ trả phí đăng ký định kỳ (SaaS / Subscription) — doanh thu định kỳ hàng tháng</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>Mô hình bán lẻ truyền thống thanh toán trực tiếp một lần tại quầy — bán lẻ một lần</v>
       </c>
-      <c r="G7" t="str">
-        <v>Mô hình đấu giá tài sản trực tuyến qua mạng internet — đấu giá tài sản</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Mô hình nhận thầu xây dựng các công trình hạ tầng kỹ thuật quốc gia — nhận thầu xây dựng</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -630,13 +630,13 @@
         <v>Phân tích và theo dõi hành vi của một nhóm người dùng có chung một đặc điểm xuất phát điểm trong một khoảng thời gian (ví dụ: nhóm khách hàng đăng ký vào tháng 1) — phân tích nhóm khách hàng đồng thời kỳ</v>
       </c>
       <c r="F8" t="str">
-        <v>Phân tích cấu trúc bảng dữ liệu của hệ quản trị cơ sở dữ liệu quan hệ — phân tích database</v>
+        <v>Biểu đồ so sánh mức độ hài lòng của khách hàng đối với 5 đối thủ cạnh tranh lớn nhất — so sánh đối thủ</v>
       </c>
       <c r="G8" t="str">
         <v>Đo lường thời gian trễ trung bình của các API kết nối với cổng thanh toán — phân tích hiệu năng hệ thống</v>
       </c>
       <c r="H8" t="str">
-        <v>Biểu đồ so sánh mức độ hài lòng của khách hàng đối với 5 đối thủ cạnh tranh lớn nhất — so sánh đối thủ</v>
+        <v>Phân tích cấu trúc bảng dữ liệu của hệ quản trị cơ sở dữ liệu quan hệ — phân tích database</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -656,19 +656,19 @@
         <v>NPS được tính dựa trên câu hỏi: "Trên thang điểm từ 0-10, khả năng bạn giới thiệu sản phẩm này cho bạn bè là bao nhiêu?". Khách hàng chọn 9-10 là Promoters (Người ủng hộ), 7-8 là Passives, 0-6 là Detractors (Người gièm pha). NPS = %Promoters - %Detractors.</v>
       </c>
       <c r="E9" t="str">
+        <v>Tổng số tiền tối đa khách hàng đã chi tiêu trên ứng dụng di động trong một năm — tổng chi tiêu khách hàng</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Tỷ lệ phần trăm khách hàng tự thực hiện đăng ký tài khoản thành công mà không cần hỗ trợ — tỷ lệ tự đăng ký</v>
+      </c>
+      <c r="G9" t="str">
         <v>Mức độ hài lòng và lòng trung thành của khách hàng thông qua khả năng họ sẵn sàng giới thiệu sản phẩm cho người khác — chỉ số đo lường lòng trung thành</v>
       </c>
-      <c r="F9" t="str">
-        <v>Tổng số tiền tối đa khách hàng đã chi tiêu trên ứng dụng di động trong một năm — tổng chi tiêu khách hàng</v>
-      </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Tốc độ tải trang trung bình của ứng dụng di động trên thiết bị của khách hàng — tốc độ ứng dụng khách</v>
       </c>
-      <c r="H9" t="str">
-        <v>Tỷ lệ phần trăm khách hàng tự thực hiện đăng ký tài khoản thành công mà không cần hỗ trợ — tỷ lệ tự đăng ký</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -688,10 +688,10 @@
         <v>Tỷ lệ $LTV : CAC \ge 3 : 1$ — giá trị vòng đời lớn hơn gấp 3 lần chi phí thu hút</v>
       </c>
       <c r="F10" t="str">
+        <v>Tỷ lệ $LTV : CAC &lt; 1 : 2$ — chi phí thu hút khách hàng lớn gấp đôi giá trị vòng đời</v>
+      </c>
+      <c r="G10" t="str">
         <v>Tỷ lệ $LTV : CAC = 1 : 1$ — doanh thu vòng đời bằng đúng chi phí bỏ ra thu hút</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Tỷ lệ $LTV : CAC &lt; 1 : 2$ — chi phí thu hút khách hàng lớn gấp đôi giá trị vòng đời</v>
       </c>
       <c r="H10" t="str">
         <v>Hai chỉ số này hoàn toàn độc lập và không có mối quan hệ tài chính nào với nhau — độc lập chỉ số</v>
@@ -714,10 +714,10 @@
         <v>ARPU (Average Revenue Per User) giúp đánh giá hiệu quả kinh doanh của sản phẩm. ARPU tăng chứng tỏ doanh nghiệp đang thực hiện tốt việc bán thêm (upsell) hoặc tăng giá trị dịch vụ cung cấp cho tập khách hàng hiện có.</v>
       </c>
       <c r="E11" t="str">
+        <v>Tổng số lượng đơn hàng chia cho tổng số lượng khách hàng đăng ký tài khoản; phản ánh tần suất mua sắm — tần suất mua hàng</v>
+      </c>
+      <c r="F11" t="str">
         <v>Tổng doanh thu chia cho tổng số lượng người dùng hoạt động (Active Users) trong một khoảng thời gian; phản ánh khả năng kiếm tiền (Monetization) trên mỗi người dùng — doanh thu trung bình trên mỗi người dùng</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Tổng số lượng đơn hàng chia cho tổng số lượng khách hàng đăng ký tài khoản; phản ánh tần suất mua sắm — tần suất mua hàng</v>
       </c>
       <c r="G11" t="str">
         <v>Tổng chi phí phát triển phần mềm chia cho tổng số lượng người dùng; phản ánh giá thành công nghệ — chi phí công nghệ bình quân</v>
@@ -726,7 +726,7 @@
         <v>Tổng số lượng đánh giá tốt chia cho tổng số lượng người dùng hoạt động; phản ánh mức độ yêu thích sản phẩm — mức độ yêu thích</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -746,13 +746,13 @@
         <v>DAU/MAU đo lường mức độ kết dính (Stickiness - tần suất người dùng quay lại hàng ngày trong tháng); Retention Rate đo lường tỷ lệ người dùng còn hoạt động sau một khoảng thời gian kể từ ngày đầu tiên sử dụng — kết dính vs giữ chân</v>
       </c>
       <c r="F12" t="str">
-        <v>DAU/MAU chỉ áp dụng cho trang web; còn Retention Rate chỉ sử dụng cho ứng dụng di động — phân loại nền tảng</v>
+        <v>DAU/MAU do phòng IT quản trị; còn Retention Rate do phòng nhân sự quản lý báo cáo — phòng ban quản lý</v>
       </c>
       <c r="G12" t="str">
         <v>DAU/MAU đo lường doanh thu tài chính; còn Retention Rate đo lường chi phí marketing — doanh thu vs chi phí</v>
       </c>
       <c r="H12" t="str">
-        <v>DAU/MAU do phòng IT quản trị; còn Retention Rate do phòng nhân sự quản lý báo cáo — phòng ban quản lý</v>
+        <v>DAU/MAU chỉ áp dụng cho trang web; còn Retention Rate chỉ sử dụng cho ứng dụng di động — phân loại nền tảng</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -772,19 +772,19 @@
         <v>Payback Period quyết định tính sống còn của dòng tiền. Ví dụ, nếu CAC = 120 USD, ARPU hàng tháng = 10 USD, thì mất 12 tháng để hoàn vốn CAC. Nếu khách hàng rời bỏ app (churn) ở tháng thứ 6, doanh nghiệp sẽ lỗ 60 USD trên khách hàng đó. Doanh nghiệp SaaS hướng tới Payback Period dưới 12 tháng.</v>
       </c>
       <c r="E13" t="str">
+        <v>Số năm cần thiết để doanh nghiệp trả hết nợ vay ngân hàng để xây dựng tòa nhà văn phòng — thời gian hoàn nợ vay</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Thời gian trung bình để đội ngũ hỗ trợ giải quyết xong một khiếu nại của khách hàng — thời gian xử lý khiếu nại</v>
+      </c>
+      <c r="G13" t="str">
         <v>Số tháng cần thiết để doanh thu từ một khách hàng bù đắp lại chi phí CAC bỏ ra để có được khách hàng đó; thời gian hoàn vốn càng ngắn giúp dòng tiền quay vòng nhanh và giảm rủi ro tài chính — thời gian hoàn vốn CAC</v>
       </c>
-      <c r="F13" t="str">
-        <v>Số năm cần thiết để doanh nghiệp trả hết nợ vay ngân hàng để xây dựng tòa nhà văn phòng — thời gian hoàn nợ vay</v>
-      </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Số ngày mà khách hàng được phép nợ tiền thanh toán hóa đơn kể từ khi nhận được hàng — thời hạn thanh toán nợ</v>
       </c>
-      <c r="H13" t="str">
-        <v>Thời gian trung bình để đội ngũ hỗ trợ giải quyết xong một khiếu nại của khách hàng — thời gian xử lý khiếu nại</v>
-      </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -833,13 +833,13 @@
         <v>Tỷ lệ doanh thu định kỳ giữ chân được từ tập khách hàng cũ sau khi đã cộng thêm doanh thu nâng cấp (Upsell) và trừ đi doanh thu mất mát do rời bỏ (Churn) — sức khỏe doanh thu từ khách hàng cũ</v>
       </c>
       <c r="F15" t="str">
-        <v>Tổng doanh thu thuần thu được từ các chiến dịch quảng cáo trực tuyến trực tiếp — doanh thu chiến dịch quảng cáo</v>
+        <v>Số lượng khách hàng đăng ký mới thông qua sự giới thiệu của khách hàng cũ — số lượng khách giới thiệu</v>
       </c>
       <c r="G15" t="str">
         <v>Tỷ lệ phần trăm lợi nhuận biên sau khi đã trừ đi toàn bộ chi phí sản xuất phần mềm — tỷ suất lợi nhuận biên</v>
       </c>
       <c r="H15" t="str">
-        <v>Số lượng khách hàng đăng ký mới thông qua sự giới thiệu của khách hàng cũ — số lượng khách giới thiệu</v>
+        <v>Tổng doanh thu thuần thu được từ các chiến dịch quảng cáo trực tuyến trực tiếp — doanh thu chiến dịch quảng cáo</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>Customer Lifetime = $1 / \text{Churn Rate}$. Với Churn Rate hàng tháng = 5% (0.05), Lifetime trung bình của khách hàng là $1 / 0.05 = 20$ tháng.</v>
       </c>
       <c r="E16" t="str">
+        <v>Không thể tính toán được nếu không có số lượng khách hàng cụ thể đầu kỳ — thiếu dữ liệu</v>
+      </c>
+      <c r="F16" t="str">
         <v>20 tháng — tính bằng công thức $1 / Churn\_Rate$ — thời gian gắn bó trung bình</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>5 tháng — dựa trên tỷ lệ phần trăm chênh lệch — thời gian gắn bó ngắn</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>50 tháng — tính theo quy mô lũy kế năm tài chính — thời gian gắn bó dài</v>
       </c>
-      <c r="H16" t="str">
-        <v>Không thể tính toán được nếu không có số lượng khách hàng cụ thể đầu kỳ — thiếu dữ liệu</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>ARR chỉ tính phần doanh thu có tính lặp lại (subscriptions). Run Rate (nhân doanh thu tháng gần nhất với 12) bao gồm cả doanh thu một lần (one-off sales, consulting fees), mang tính chất dự đoán giả định tương lai có thể không phản ánh đúng thực tế nếu có tính mùa vụ.</v>
       </c>
       <c r="E17" t="str">
+        <v>ARR chỉ dùng cho doanh nghiệp phần cứng; còn Run Rate chỉ dùng cho doanh nghiệp phần mềm — phân loại doanh nghiệp</v>
+      </c>
+      <c r="F17" t="str">
         <v>ARR là doanh thu định kỳ năm từ các hợp đồng subscription hoạt động; Run Rate là doanh thu dự phóng cả năm dựa trên kết quả doanh thu của một tháng/quý gần nhất nhân lên — doanh thu định kỳ thực tế vs doanh thu dự phóng</v>
       </c>
-      <c r="F17" t="str">
-        <v>ARR chỉ dùng cho doanh nghiệp phần cứng; còn Run Rate chỉ dùng cho doanh nghiệp phần mềm — phân loại doanh nghiệp</v>
-      </c>
       <c r="G17" t="str">
+        <v>ARR luôn luôn có giá trị lớn gấp 12 lần so với Run Rate Revenue — so sánh quy mô chỉ số</v>
+      </c>
+      <c r="H17" t="str">
         <v>ARR bắt buộc phải được kiểm toán bởi chính phủ; còn Run Rate do doanh nghiệp tự công bố nội bộ — tính pháp lý</v>
       </c>
-      <c r="H17" t="str">
-        <v>ARR luôn luôn có giá trị lớn gấp 12 lần so với Run Rate Revenue — so sánh quy mô chỉ số</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>NPS được tính bằng %Promoters - %Detractors. Trường hợp tệ nhất là 100% người dùng là Detractors (NPS = -100). Trường hợp tốt nhất là 100% người dùng là Promoters (NPS = +100). NPS trên 50 được coi là xuất sắc.</v>
       </c>
       <c r="E18" t="str">
+        <v>Từ 0% đến 100% — tỷ lệ phần trăm phân bổ khách hàng ủng hộ</v>
+      </c>
+      <c r="F18" t="str">
         <v>Từ -100 đến +100 — thang điểm đánh giá lòng trung thành</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Từ 0 đến 10 — thang điểm đánh giá mức độ hài lòng đơn giản</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Từ 0% đến 100% — tỷ lệ phần trăm phân bổ khách hàng ủng hộ</v>
       </c>
       <c r="H18" t="str">
         <v>Từ -1 đến +1 — hệ số tương quan tuyến tính của lòng trung thành</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -952,10 +952,10 @@
         <v>Tỷ lệ LTV : CAC = 4 : 1; mô hình kinh doanh cực kỳ xuất sắc vì vượt qua mốc 3:1, doanh nghiệp nên tăng cường đầu tư mạnh vào marketing — LTV:CAC = 4:1 xuất sắc</v>
       </c>
       <c r="G19" t="str">
+        <v>Tỷ lệ LTV : CAC = 3 : 1; mô hình đạt trạng thái cân bằng hoàn hảo, không cần thay đổi bất kỳ chiến lược nào — LTV:CAC = 3:1 cân bằng</v>
+      </c>
+      <c r="H19" t="str">
         <v>Tỷ lệ LTV : CAC = 0.8 : 1; doanh nghiệp đang bị lỗ trực tiếp trên mỗi khách hàng có được, cần phải tăng giá thuê bao ngay lập tức — LTV:CAC = 0.8:1 lỗ trực tiếp</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Tỷ lệ LTV : CAC = 3 : 1; mô hình đạt trạng thái cân bằng hoàn hảo, không cần thay đổi bất kỳ chiến lược nào — LTV:CAC = 3:1 cân bằng</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>Nếu đường cong Retention tiếp tục dốc xuống về 0, app của bạn đang bị rò rỉ khách hàng (leaky bucket) và sẽ chết. Nếu đường cong đi ngang và ổn định ở một mức (ví dụ 20% kể từ tháng thứ 3 trở đi), điều đó chứng tỏ bạn đã giữ chân được một lượng người dùng trung thành ổn định, là dấu hiệu đạt Product-Market Fit.</v>
       </c>
       <c r="E20" t="str">
-        <v>Sản phẩm đã đạt được mức độ phù hợp thị trường (Product-Market Fit) đối với một tập khách hàng trung thành nhất định; tỷ lệ giữ chân ổn định ở mức dài hạn — đạt PMF ổn định dài hạn</v>
+        <v>Doanh nghiệp sắp bị phá sản do lượng người dùng mới đăng ký hàng tháng giảm về mức 0 — suy giảm tăng trưởng</v>
       </c>
       <c r="F20" t="str">
         <v>Sản phẩm đang bị lỗi kỹ thuật nghiêm trọng trên production khiến người dùng không thể đăng xuất tài khoản — lỗi hệ thống</v>
       </c>
       <c r="G20" t="str">
-        <v>Doanh nghiệp sắp bị phá sản do lượng người dùng mới đăng ký hàng tháng giảm về mức 0 — suy giảm tăng trưởng</v>
+        <v>Sản phẩm đã đạt được mức độ phù hợp thị trường (Product-Market Fit) đối với một tập khách hàng trung thành nhất định; tỷ lệ giữ chân ổn định ở mức dài hạn — đạt PMF ổn định dài hạn</v>
       </c>
       <c r="H20" t="str">
         <v>Toàn bộ khách hàng cũ đã chuyển sang sử dụng dịch vụ của đối thủ cạnh tranh trực tiếp trên thị trường — mất khách hàng</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Rất nhiều startup chết vì đặt ngân sách CAC dựa trên LTV thô (doanh thu). Ví dụ: LTV thô = 100 USD, biên lợi nhuận (Gross Margin) chỉ đạt 20% (Net LTV = 20 USD). Nếu thiết lập trần CAC = 40 USD (dựa trên suy nghĩ LTV 100 USD &gt; 40 USD), công ty thực tế đang lỗ ròng 20 USD trên mỗi khách hàng mới.</v>
       </c>
       <c r="E21" t="str">
+        <v>LTV thô bắt buộc phải lớn gấp 100 lần so với Net LTV trong mọi mô hình kinh doanh bán lẻ — quy mô chênh lệch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>LTV thô do phòng Marketing tính toán; Net LTV do phòng IT tự động lập trình trên máy chủ — phân vai trò tính</v>
+      </c>
+      <c r="G21" t="str">
+        <v>LTV thô chỉ dùng cho khách hàng nam; Net LTV chỉ áp dụng cho khách hàng nữ — phân loại khách hàng</v>
+      </c>
+      <c r="H21" t="str">
         <v>LTV thô chỉ tính tổng doanh thu; Net LTV trừ đi giá vốn hàng bán (COGS) và chi phí vận hành; dùng LTV thô để đặt trần chi phí CAC sẽ khiến doanh nghiệp chi tiêu quá tay cho marketing và thực tế bị lỗ ròng — rủi ro thổi phồng ngân sách marketing</v>
       </c>
-      <c r="F21" t="str">
-        <v>LTV thô chỉ dùng cho khách hàng nam; Net LTV chỉ áp dụng cho khách hàng nữ — phân loại khách hàng</v>
-      </c>
-      <c r="G21" t="str">
-        <v>LTV thô do phòng Marketing tính toán; Net LTV do phòng IT tự động lập trình trên máy chủ — phân vai trò tính</v>
-      </c>
-      <c r="H21" t="str">
-        <v>LTV thô bắt buộc phải lớn gấp 100 lần so với Net LTV trong mọi mô hình kinh doanh bán lẻ — quy mô chênh lệch</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>SaaS Quick Ratio đo lường hiệu quả tăng trưởng ARR. Nó so sánh phần ARR tăng thêm (khách mới + upsell khách cũ) với phần ARR bị mất đi (khách hạ gói + khách hủy thuê bao). Tỷ lệ Quick Ratio &gt; 4 chứng tỏ tốc độ tăng trưởng nhanh gấp 4 lần tốc độ mất mát doanh thu, thể hiện doanh nghiệp phát triển cực kỳ khỏe mạnh.</v>
       </c>
       <c r="E22" t="str">
+        <v>$\text{Quick Ratio} = \text{Tốc độ tải trang chủ} / \text{Tốc độ tải trang thanh toán}$; đo lường hiệu năng tải trang web — tốc độ tải trang</v>
+      </c>
+      <c r="F22" t="str">
         <v>$\text{Quick Ratio} = (\text{New ARR} + \text{Expansion ARR}) / (\text{Contraction ARR} + \text{Churn ARR})$; thể hiện khả năng tăng trưởng doanh thu định kỳ bất chấp sự mất mát khách hàng (Quick Ratio &gt; 4 được coi là xuất sắc) — chỉ số đo lường hiệu năng tăng trưởng ARR</v>
-      </c>
-      <c r="F22" t="str">
-        <v>$\text{Quick Ratio} = \text{Tổng tài sản ngắn hạn} / \text{Tổng nợ ngắn hạn}$; đo lường khả năng thanh toán nhanh các khoản nợ của doanh nghiệp — thanh toán tài chính doanh nghiệp</v>
       </c>
       <c r="G22" t="str">
         <v>$\text{Quick Ratio} = \text{Số lượng bug được sửa trong ngày} / \text{Tổng số lượng bug phát sinh}$; đo lường năng suất sửa lỗi của dev — năng suất sửa bug</v>
       </c>
       <c r="H22" t="str">
-        <v>$\text{Quick Ratio} = \text{Tốc độ tải trang chủ} / \text{Tốc độ tải trang thanh toán}$; đo lường hiệu năng tải trang web — tốc độ tải trang</v>
+        <v>$\text{Quick Ratio} = \text{Tổng tài sản ngắn hạn} / \text{Tổng nợ ngắn hạn}$; đo lường khả năng thanh toán nhanh các khoản nợ của doanh nghiệp — thanh toán tài chính doanh nghiệp</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Công thức K-factor: $K = c \cdot i$, với $c$ là số lời mời trung bình gửi đi bởi 1 khách hàng, $i$ là tỷ lệ chuyển đổi lời mời thành công. Nếu $K = 1.2$ ($&gt;1$), cứ 100 người dùng ban đầu sẽ tự động mời được 120 người mới, 120 người đó mời tiếp 144 người... tạo ra hiệu ứng lan truyền (Virality) khổng lồ.</v>
       </c>
       <c r="E23" t="str">
+        <v>K-factor đo lường số lần người dùng mở ứng dụng di động trong một giờ cao điểm — tần suất mở ứng dụng</v>
+      </c>
+      <c r="F23" t="str">
+        <v>K-factor đo lường dung lượng lưu trữ trung bình của ứng dụng khi cài đặt trên điện thoại di động — dung lượng cài đặt</v>
+      </c>
+      <c r="G23" t="str">
+        <v>K-factor đo lường số lượng lỗi kỹ thuật phát sinh trên mỗi 1000 dòng code của lập trình viên — chỉ số lỗi code</v>
+      </c>
+      <c r="H23" t="str">
         <v>K-factor đo lường số lượng người dùng mới được mời thành công bởi mỗi người dùng hiện tại; nếu $K &gt; 1$, ứng dụng sẽ tự động tăng trưởng theo cấp số nhân một cách tự nhiên mà không cần chạy ads quảng cáo — hệ số lan truyền virus</v>
       </c>
-      <c r="F23" t="str">
-        <v>K-factor đo lường số lượng lỗi kỹ thuật phát sinh trên mỗi 1000 dòng code của lập trình viên — chỉ số lỗi code</v>
-      </c>
-      <c r="G23" t="str">
-        <v>K-factor đo lường dung lượng lưu trữ trung bình của ứng dụng khi cài đặt trên điện thoại di động — dung lượng cài đặt</v>
-      </c>
-      <c r="H23" t="str">
-        <v>K-factor đo lường số lần người dùng mở ứng dụng di động trong một giờ cao điểm — tần suất mở ứng dụng</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1094,10 +1094,10 @@
         <v>Vì doanh thu thô chưa trừ đi giá vốn hàng bán và chi phí vận hành trực tiếp; dùng doanh thu thô làm thời gian hoàn vốn thực tế trên giấy tờ có vẻ ngắn nhưng doanh nghiệp vẫn có thể bị cạn kiệt dòng tiền mặt thực tế — tính toán hoàn vốn dựa trên lợi nhuận gộp</v>
       </c>
       <c r="F24" t="str">
+        <v>Vì doanh thu thô bắt buộc phải được quy đổi sang đồng tiền USD trước khi thực hiện tính toán hoàn vốn — quy đổi tiền tệ</v>
+      </c>
+      <c r="G24" t="str">
         <v>Vì lợi nhuận gộp là chỉ số phi chức năng còn doanh thu thô luôn là chỉ số chức năng kinh doanh — phân loại chỉ số</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Vì doanh thu thô bắt buộc phải được quy đổi sang đồng tiền USD trước khi thực hiện tính toán hoàn vốn — quy đổi tiền tệ</v>
       </c>
       <c r="H24" t="str">
         <v>Vì thời gian hoàn vốn chỉ được phép tính toán đối với các dự án đã hoạt động trên 10 năm — giới hạn tuổi dự án</v>
@@ -1120,19 +1120,19 @@
         <v>NRR &lt; 100% (ở đây là 75%) có nghĩa là doanh nghiệp đang bị mất đi 25% doanh thu từ tập khách hàng cũ sau mỗi năm (do họ hủy gói hoặc giảm cấp dịch vụ). Tăng trưởng nhanh nhờ khách mới chỉ là bề nổi che lấp sự rò rỉ dữ liệu. Khi chi phí mua khách mới (CAC) tăng lên hoặc cạn kiệt thị trường, doanh nghiệp sẽ sụp đổ nhanh chóng.</v>
       </c>
       <c r="E25" t="str">
+        <v>Doanh nghiệp đang vận hành cực kỳ khỏe mạnh và bền vững do số lượng khách hàng mới tăng trưởng liên tục — đánh giá bề mặt sai lệch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Doanh nghiệp sắp đạt mốc IPO trên sàn chứng khoán quốc tế nhờ doanh thu tăng trưởng ổn định — nhận định lạc quan quá mức</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Sản phẩm đã đạt mốc Product-Market Fit hoàn hảo và không cần cải tiến thêm bất kỳ tính năng nào — nhận định sai thực tế</v>
+      </c>
+      <c r="H25" t="str">
         <v>Doanh nghiệp đang gặp vấn đề nghiêm trọng về giữ chân khách hàng (High Churn Rate ở tập khách hàng cũ); sự tăng trưởng hiện tại chỉ dựa vào việc đốt tiền mua khách mới để lấp đầy lỗ hổng (Leaky Bucket) — tăng trưởng không bền vững do Churn cao</v>
       </c>
-      <c r="F25" t="str">
-        <v>Doanh nghiệp đang vận hành cực kỳ khỏe mạnh và bền vững do số lượng khách hàng mới tăng trưởng liên tục — đánh giá bề mặt sai lệch</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Doanh nghiệp sắp đạt mốc IPO trên sàn chứng khoán quốc tế nhờ doanh thu tăng trưởng ổn định — nhận định lạc quan quá mức</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Sản phẩm đã đạt mốc Product-Market Fit hoàn hảo và không cần cải tiến thêm bất kỳ tính năng nào — nhận định sai thực tế</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Độ co giãn của cầu theo giá giúp doanh nghiệp đưa ra chiến lược định giá (Pricing Strategy) khoa học. Cầu co giãn ($|E| &gt; 1$) nghĩa là khách hàng rất nhạy cảm với giá (ví dụ: tăng giá 10% làm giảm 20% lượng mua, dẫn đến tổng doanh thu giảm). Cầu ít co giãn ($|E| &lt; 1$, như thuốc chữa bệnh) cho phép tăng giá để tăng tổng doanh thu.</v>
       </c>
       <c r="E26" t="str">
+        <v>Đo lường tốc độ giao hàng trung bình của chuỗi cung ứng khi giá xăng dầu biến động — tốc độ vận chuyển chuỗi cung ứng</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Tính toán số lượng nhân viên tối đa cần sa thải để duy trì lợi nhuận ròng ổn định cho công ty — tối ưu hóa nhân sự</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Đo lường chi phí sản xuất trung bình của một sản phẩm khi số lượng đặt hàng tăng lên — hiệu ứng quy mô sản xuất</v>
+      </c>
+      <c r="H26" t="str">
         <v>Đo lường mức độ nhạy cảm của nhu cầu lượng mua sản phẩm khi giá bán thay đổi; nếu $|E| &gt; 1$ (cầu co giãn), việc tăng giá sẽ làm giảm tổng doanh thu do lượng cầu giảm mạnh hơn tốc độ tăng giá — độ co giãn của cầu theo giá</v>
       </c>
-      <c r="F26" t="str">
-        <v>Đo lường chi phí sản xuất trung bình của một sản phẩm khi số lượng đặt hàng tăng lên — hiệu ứng quy mô sản xuất</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Đo lường tốc độ giao hàng trung bình của chuỗi cung ứng khi giá xăng dầu biến động — tốc độ vận chuyển chuỗi cung ứng</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Tính toán số lượng nhân viên tối đa cần sa thải để duy trì lợi nhuận ròng ổn định cho công ty — tối ưu hóa nhân sự</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
